--- a/Dataset/Masalah Kulit Tidak Cocok.xlsx
+++ b/Dataset/Masalah Kulit Tidak Cocok.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAGw\backend\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1541767B-05C4-4DE9-86A2-203EE5832755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C3ADDE-0311-4E60-BB5A-E87FB5BD13EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="388">
   <si>
     <t>Ingredient</t>
   </si>
@@ -892,9 +892,6 @@
     <t>Lapisan oklusif tebal yang ditinggalkannya di atas wajah justru dapat memerangkap debu, sel kulit mati, dan kotoran udara, membuat wajah tampak makin kusam dan dekil.</t>
   </si>
   <si>
-    <t>Jerawat Aktif</t>
-  </si>
-  <si>
     <t>SANGAT DILARANG. Gesekan dari partikel scrub kasar ini dapat memecahkan dinding pustul/papul jerawat, menyebarkan bakteri penyebab jerawat ke area sekitarnya, memperparah inflamasi, dan memicu infeksi sekunder.</t>
   </si>
   <si>
@@ -1013,9 +1010,6 @@
   </si>
   <si>
     <t>Risiko Iritasi Pasca-Inflamasi. Jika eksfoliasi asam ini memicu over-peeling atau iritasi kronis akibat tidak dilindungi tabir surya, kondisi tersebut justru akan memperparah flek hitam (PIH).</t>
-  </si>
-  <si>
-    <t>Jerawat Meradang</t>
   </si>
   <si>
     <t>Risiko Eksaserbasi Inflamasi. Sensasi dingin yang terlalu kuat pada dinding jerawat pustul yang tipis dapat merusak jaringan kulit sekitarnya dan memperpanjang masa pemulihan luka.</t>
@@ -5663,13 +5657,13 @@
     </row>
     <row r="123" spans="1:26" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
-        <v>290</v>
+        <v>156</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>67</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
@@ -5703,7 +5697,7 @@
         <v>67</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
@@ -5737,7 +5731,7 @@
         <v>68</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
@@ -5771,7 +5765,7 @@
         <v>69</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
@@ -5805,7 +5799,7 @@
         <v>114</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
@@ -5839,7 +5833,7 @@
         <v>70</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
@@ -5873,7 +5867,7 @@
         <v>71</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
@@ -5907,7 +5901,7 @@
         <v>72</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
@@ -5941,7 +5935,7 @@
         <v>73</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
@@ -5975,7 +5969,7 @@
         <v>74</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
@@ -6009,7 +6003,7 @@
         <v>75</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
@@ -6043,7 +6037,7 @@
         <v>76</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
@@ -6077,7 +6071,7 @@
         <v>115</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
@@ -6111,7 +6105,7 @@
         <v>116</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
@@ -6145,7 +6139,7 @@
         <v>77</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
@@ -6179,7 +6173,7 @@
         <v>78</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
@@ -6213,7 +6207,7 @@
         <v>79</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
@@ -6247,7 +6241,7 @@
         <v>81</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
@@ -6281,7 +6275,7 @@
         <v>80</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
@@ -6315,7 +6309,7 @@
         <v>82</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
@@ -6349,7 +6343,7 @@
         <v>117</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
@@ -6383,7 +6377,7 @@
         <v>119</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
@@ -6417,7 +6411,7 @@
         <v>118</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
@@ -6451,7 +6445,7 @@
         <v>120</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
@@ -6485,7 +6479,7 @@
         <v>83</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
@@ -6519,7 +6513,7 @@
         <v>84</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
@@ -6553,7 +6547,7 @@
         <v>121</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
@@ -6587,7 +6581,7 @@
         <v>85</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
@@ -6621,7 +6615,7 @@
         <v>86</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
@@ -6655,7 +6649,7 @@
         <v>122</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
@@ -6689,7 +6683,7 @@
         <v>123</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
@@ -6723,7 +6717,7 @@
         <v>87</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
@@ -6757,7 +6751,7 @@
         <v>88</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
@@ -6791,7 +6785,7 @@
         <v>89</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
@@ -6825,7 +6819,7 @@
         <v>163</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
@@ -6859,7 +6853,7 @@
         <v>124</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
@@ -6893,7 +6887,7 @@
         <v>125</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
@@ -6927,7 +6921,7 @@
         <v>126</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
@@ -6961,7 +6955,7 @@
         <v>128</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
@@ -6995,7 +6989,7 @@
         <v>127</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
@@ -7023,13 +7017,13 @@
     </row>
     <row r="163" spans="1:26" ht="15.75" customHeight="1">
       <c r="A163" s="6" t="s">
-        <v>331</v>
+        <v>156</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
@@ -7063,7 +7057,7 @@
         <v>129</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
@@ -7097,7 +7091,7 @@
         <v>130</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
@@ -7131,7 +7125,7 @@
         <v>91</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
@@ -7165,7 +7159,7 @@
         <v>131</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
@@ -7199,7 +7193,7 @@
         <v>164</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
@@ -7233,7 +7227,7 @@
         <v>92</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
@@ -7267,7 +7261,7 @@
         <v>93</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
@@ -7301,7 +7295,7 @@
         <v>132</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
@@ -7335,7 +7329,7 @@
         <v>133</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
@@ -7369,7 +7363,7 @@
         <v>94</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
@@ -7403,7 +7397,7 @@
         <v>134</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
@@ -7437,7 +7431,7 @@
         <v>135</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
@@ -7471,7 +7465,7 @@
         <v>95</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
@@ -7505,7 +7499,7 @@
         <v>137</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
@@ -7539,7 +7533,7 @@
         <v>136</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
@@ -7570,10 +7564,10 @@
         <v>154</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
@@ -7607,7 +7601,7 @@
         <v>96</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
@@ -7641,7 +7635,7 @@
         <v>138</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
@@ -7675,7 +7669,7 @@
         <v>97</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
@@ -7709,7 +7703,7 @@
         <v>139</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
@@ -7743,7 +7737,7 @@
         <v>98</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
@@ -7777,7 +7771,7 @@
         <v>165</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
@@ -7811,7 +7805,7 @@
         <v>99</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
@@ -7845,7 +7839,7 @@
         <v>140</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
@@ -7879,7 +7873,7 @@
         <v>166</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
@@ -7913,7 +7907,7 @@
         <v>141</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
@@ -7947,7 +7941,7 @@
         <v>142</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
@@ -7978,10 +7972,10 @@
         <v>154</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
@@ -8015,7 +8009,7 @@
         <v>100</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
@@ -8046,10 +8040,10 @@
         <v>154</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
@@ -8080,10 +8074,10 @@
         <v>154</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
@@ -8117,7 +8111,7 @@
         <v>143</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
@@ -8185,7 +8179,7 @@
         <v>145</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
@@ -8219,7 +8213,7 @@
         <v>144</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
@@ -8253,7 +8247,7 @@
         <v>101</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
@@ -8287,7 +8281,7 @@
         <v>146</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
@@ -8318,10 +8312,10 @@
         <v>156</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
@@ -8355,7 +8349,7 @@
         <v>147</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
@@ -8389,7 +8383,7 @@
         <v>148</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
@@ -8423,7 +8417,7 @@
         <v>102</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
@@ -8457,7 +8451,7 @@
         <v>103</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
@@ -8491,7 +8485,7 @@
         <v>149</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
@@ -8525,7 +8519,7 @@
         <v>150</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
@@ -8556,10 +8550,10 @@
         <v>154</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
@@ -8593,7 +8587,7 @@
         <v>104</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
@@ -8627,7 +8621,7 @@
         <v>105</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
@@ -8661,7 +8655,7 @@
         <v>151</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
@@ -8695,7 +8689,7 @@
         <v>106</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
@@ -8729,7 +8723,7 @@
         <v>108</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
@@ -8763,7 +8757,7 @@
         <v>107</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
@@ -8797,7 +8791,7 @@
         <v>109</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
